--- a/pixtral-12b-2409.xlsx
+++ b/pixtral-12b-2409.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3550,6 +3550,3636 @@
       <c r="AG19" t="inlineStr">
         <is>
           <t>There was a significant change in the vessel's position before and after the incident. The vessel was swept into a cove and grounded on the rocks. The distance traveled before the incident is not mentioned, but the change in position can be approximated as the distance from the fishing area to the cove at Melrose Point. This distance is not specified in the context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ondar Fishing Company Limited</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>North-west Spain</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>- (Information not provided in the context)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>- (No notable mechanical failures reported)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Yes, "Mayday" calls and activating the Digital Selective Calling (DSC) alarm at about 1935</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>North Atlantic</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Standing on the lid of a storage locker above the vessel’s main deck, in line with the top of the bulwarks; holding on to a bight of buoy line.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>- (No specific information provided about the retrieval of safety equipment)</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>"The skipper drove Eder Sands ahead prior to reversing the vessel’s course. As he did so, some of the crew briefly spotted the deckhand in the water close to a marker buoy; his head was visible, but they could not see his lifejacket. The skipper manoeuvred Eder Sands back to an inflated, but unoccupied, lifejacket was quickly blown away across the surface of the water in simulated winds and that an unlit lifejacket was almost impossible to see in the dark unless one of its retroreflective strips was directly illuminated by a light."</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>- (No information provided about previous accidents or incidents involving the vessel)</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>- (No information provided about the security of the vessel's cargo)</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>- (No information provided about the crew's training for handling emergency situations)</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>20 people, a Spanish master, mate, chief engineer and bosun and 16 Indonesian nationals</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Good visibility</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed. The vessel was operating at about 5 knots before the incident. Assuming the normal operational speed was higher, the percentage decrease in speed can be calculated as follows:</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for 26 days before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>- (Information not provided in the context)</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>- (Information not provided in the context)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ondar Fishing Company Limited</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>North-west Spain</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>- (Information not provided in the context)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>- (Information not provided in the context)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Yes, "Mayday" calls and activating the Digital Selective Calling (DSC) alarm at about 1935</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>North Atlantic</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Standing on the lid of a storage locker above the vessel’s main deck, in line with the top of the bulwarks; holding on to a bight of buoy line.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>- (The context does not provide specific information on where the crew member retrieved safety equipment from onboard the vessel.)</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on previous accidents or incidents involving the vessel.)</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the vessel's cargo security at the time of the incident.)</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the crew's training for handling emergency situations.)</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>20 people: a Spanish master, mate, chief engineer and bosun and 16 Indonesian nationals.</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>- (Information not provided)</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>- (Information not provided)</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>- (Information not provided)</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Good visibility</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed. The normal operational speed was 5 knots, and it was stopped using astern power. The percentage decrease in speed is 100%.</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for 26 days before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>- (The total cargo weight onboard at the time of the incident is not mentioned in the context)</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>- (There is no mention of a significant change in the vessel's position before and after the incident)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wheelhouse</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Long 1.2m northerly swell; air temperature 12°C; wind south-westerly force 3; sea temperature approximately 15°C</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Accessing the working deck to free a snag in the fourth fleet of creels as it was being deployed from the vessel</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>St Abbs Inshore Rescue</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>0736</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>&lt; 5 nm</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>The visibility was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed before the incident.</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 2 hours and 35 minutes before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Yes, there was a significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Wheelhouse</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Long 1.2m northerly swell; air temperature 12°C; wind south-westerly force 3; sea temperature approximately 15°C</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Accessing the working deck to free a snag in the fourth fleet of creels as it was being deployed from the vessel</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>St Abbs Inshore Rescue</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>0736</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>&lt; 5 nm</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>The visibility was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed before the incident.</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 2 hours and 35 minutes before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Yes, there was a significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>William Traynor</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>The vessel was built in 1996.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Yes, the accident had fatalities.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No, there was no distress signal or emergency call sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>River Hamble</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Light northerly wind; drizzle; 10°C.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sitting in the cockpit with the canopy closed, drinking beer.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Each drank half of their bottle of beer.</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>11 January 2022 in the early evening</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2 people: Emma Louise's owner, William Traynor, and his brother-in-law, Martin Steventon</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>- (No deviation mentioned)</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>- (No specific time mentioned for distress signal reception or emergency response)</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>- (No other vessels mentioned nearby)</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Visibility: drizzle</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Speed reduction: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Hours at sea: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Cargo weight: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Position change: Not mentioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>William Traynor</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>The vessel was built in 1996.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Yes, the accident had fatalities.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No, there was no distress signal or emergency call sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>River Hamble</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Light northerly wind; drizzle; 10°C.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sitting in the cockpit with the canopy closed, drinking beer.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Half of their bottle of beer.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>11 January 2022 in the early evening</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2 people: Emma Louise's owner and his brother-in-law</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>- (No deviation mentioned)</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>- (No specific time mentioned for distress signal reception)</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>- (No other vessels mentioned)</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Visibility: drizzle</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Speed reduction: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Hours at sea: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Cargo weight: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Position change: Not mentioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Mr. Robertson</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mallaig, Scotland</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>- (No routine activity mentioned)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6.5 knots</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>The vessel was built in 1959.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Yes, there was 1 fatality.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Yes, a distress call was sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Sound of Rùm</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Force 6 north wind, short steep swell causing heavy rolling</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sorting and stowing prawns, pulling in the net</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Ronja Harvester</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Foredeck</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Yes, distress call on VHF channel 16 at 1906</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>- (No information provided)</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>No, the nets were not routinely lashed down</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>No, the crew had not practiced man overboard recovery drills</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>1850 GMT+1</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>3 people onboard: Skipper, Senior Deckhand, Junior Deckhand</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1 hour 10 minutes</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Visibility is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed.</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 1.5 hours before the incident.</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>There was no significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mallaig, Scotland</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>- (No routine activity mentioned)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6.5 knots</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>The vessel was built in 1959.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Yes, there was 1 fatality.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Yes, the vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>No, there were no notable mechanical failures reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Yes, a distress call was sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Sound of Rùm</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Force 6 north wind, short steep swell causing heavy rolling</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sorting and stowing prawns, pulling the net inboard by hand</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Ronja Harvester</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Foredeck</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Yes, distress call on VHF channel 16 at 1906</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>- (No information provided)</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>No, the nets were not routinely lashed at the end of the day's fishing</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>No, the crew had not practiced man overboard recovery and were unfamiliar with the vessel's man overboard recovery equipment</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>1850 GMT+1</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>3 people: Skipper, Senior Deckhand, Junior Deckhand</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1 hour 10 minutes</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Visibility is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed.</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 1 hour and 50 minutes before the incident.</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Total cargo weight onboard is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>There was no significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Joe Masson</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Cairnbulg Briggs reef</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2004.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Yes, there was one presumed fatality.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No, there was no distress signal or emergency call sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Using engine power to free snagged creels</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>RNLI (Royal National Lifeboat Institution)</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Yes, previous deficiencies in safety equipment and lack of valid Short Range Certificate for VHF radio equipment.</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>- (No distress signal was received)</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>- (No other vessels were observed in the vicinity)</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Visibility: good</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Speed reduction: not mentioned</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Hours at sea: not mentioned</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Total cargo weight: not mentioned</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Position change: not mentioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2004.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Yes, there was one presumed fatality.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>No, there was no distress signal or emergency call sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Using engine power to free snagged creels</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>RNLI (Royal National Lifeboat Institution)</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Yes, previous deficiencies in safety equipment and lack of risk assessments.</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Visibility: good</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Vessel speed reduction: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Hours at sea before the incident: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Total cargo weight onboard: Not mentioned</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Significant change in the vessel's position: Not mentioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>**Inshore coastal waters**</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>**Wind force 3, waves up to 1m**</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>**lowered the multibeam echo sounder (MBES) gantry from its stowed position into the sea**</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>**rigid inflatable boats (RIB)**</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2001.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>- (No fatalities reported)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>- (No notable mechanical failures reported before the incident)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Yes, a distress signal or emergency call was sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>liferaft</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>VHF "Mayday!" call, mobile phone to report the emergency to the supervisor ashore, 999 to notify the coastguard</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>- (No previous accidents or incidents involving this vessel mentioned in the context)</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>- (No information provided about the vessel's cargo)</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Yes (The crew managed the emergency creditably, wore PFDs, and were familiar with lifesaving equipment)</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2 (skipper and a crew member)</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the deviation from the planned route)</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>14 minutes</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the distance to the nearest vessel)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Visibility was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed.</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 30 minutes before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Total cargo weight onboard at the time of the incident: 0 kg (no cargo mentioned)</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Yes, there was a significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lynmouth, North Devon, England</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Wind force 3, waves up to 1m</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>lowered the multibeam echo sounder (MBES) gantry from its stowed position into the sea</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>rigid inflatable boats (RIB)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2001.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>- (No fatalities reported)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>- (No notable mechanical failures reported before the incident)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yes, a distress signal or emergency call was sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>liferaft</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>VHF "Mayday!" call, mobile phone to report the emergency to the supervisor ashore, 999 to notify the coastguard</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>- (No previous accidents or incidents involving this vessel mentioned in the context)</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>- (No information provided about the vessel's cargo)</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>- (No information provided about the crew's training for handling emergency situations)</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2 (skipper and a crew member)</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the deviation from the planned route)</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>14 minutes</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on other vessels nearby)</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Visibility was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed.</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 1 hour before the incident.</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident was 0 kg.</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>There was no significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>- (The context does not provide specific weather conditions)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Shooting creels</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>- (The context does not mention what the crew member consumed)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>- (The context does not mention any specific type or model of rescue boat)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>When was the vessel built?</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Did the accident have any fatalities?</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Was the vessel operating under normal conditions when the incident occurred?</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Were there any notable mechanical failures reported before the incident?</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Was there any distress signal or emergency call sent out prior to the incident?</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>**Wheelhouse and next to the hauler**</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>**Yes**</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>The visibility at the time of the accident is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>The vessel did not experience a reduction in speed before the incident.</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>The time the vessel had been at sea before the incident occurred is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>There was no significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>- (The context does not provide specific weather conditions)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Shooting creels</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>- (The context does not mention what the crew member consumed)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>- (The context does not mention any specific type or model of rescue boat involved in the response)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>When was the vessel built?</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Did the accident have any fatalities?</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Was the vessel operating under normal conditions when the incident occurred?</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Were there any notable mechanical failures reported before the incident?</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Was there any distress signal or emergency call sent out prior to the incident?</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>**Wheelhouse and next to the hauler**</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>**Yes**</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>The visibility at the time of the accident is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>The vessel did not experience a reduction in speed before the incident.</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>The time the vessel had been at sea before the incident is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>There was no significant change in the vessel's position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>**6. When was the vessel built?**</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>**7. Did the accident have any fatalities?**</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>**8. Was the vessel operating under normal conditions when the incident occurred?**</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>**9. Were there any notable mechanical failures reported before the incident?**</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>**10. Was there any distress signal or emergency call sent out prior to the incident?**</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>SSE force 2 to 3, slight sea, low swell, overcast, poor visibility in patchy fog</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Talis’s chief officer (C/O) was carrying out administrative navigation duties at the chart table and the bridge computer. The able-bodied seaman (AB) was on the port side between the closed bridge wing door and the centre steering console.</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>RNLI all-weather lifeboat (ALB)</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>- (No information provided about the retrieval of safety equipment)</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Yes, Achieve's skipper called Humber Coastguard on VHF radio channel 16 to inform them of the collision and his predicament with flooding.</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>- (No information provided about previous accidents or incidents involving the vessels)</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>- (No information provided about the cargo secure status)</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>- (No information provided about the crew's training for handling emergency situations)</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2 (skipper and deckhand)</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>- (not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>- (not mentioned)</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>1nm (distance to the bulk carrier anchored off Tynemouth)</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>The visibility was restricted due to fog patches.</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>No, the vessel did not experience a reduction in speed before the incident.</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Achieve had been at sea for approximately 6 hours and 38 minutes before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard Talis at the time of the incident was 2646 tons.</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>The distance traveled by Talis before the incident was approximately 10.5 nautical miles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>**6. When was the vessel built?**</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>**7. Did the accident have any fatalities?**</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>**8. Was the vessel operating under normal conditions when the incident occurred?**</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>**9. Were there any notable mechanical failures reported before the incident?**</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>**10. Was there any distress signal or emergency call sent out prior to the incident?**</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>SSE force 2 to 3, slight sea, low swell, overcast, poor visibility in patchy fog</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Talis’s chief officer (C/O) was carrying out administrative navigation duties at the chart table and the bridge computer. The able-bodied seaman (AB) was on the port side between the closed bridge wing door and the centre steering console.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>RNLI all-weather lifeboat (ALB)</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>"Humber Coastguard on very high frequency (VHF) radio channel 16"</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>'-'</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>"Both the skipper and the deckhand had completed all UK statutory safety courses... In addition, the deckhand held a non-mandatory under 16.5m skipper’s certificate"</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2 (skipper and deckhand)</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>- (not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>- (not mentioned)</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>1nm (distance to the bulk carrier anchored off Tynemouth)</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>The visibility was described as "restricted visibility" and "fog patches." No specific distance is provided.</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>No, the vessel did not experience a reduction in speed before the incident.</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Achieve had been at sea since about 0530 UTC, so approximately 10 hours and 15 minutes before the incident at 1541 UTC.</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>The cargo weight onboard Talis was not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>No significant change in the vessel's position was mentioned in the context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Irish Sea</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Wind: easterly Beaufort force 3 to 4, Sea water temperature: 15.3°C</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Running the boat, steering</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>RNLI inshore lifeboat</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>cabin space</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Yes, the crew contacted the coastguard and Fivebuoys' skipper.</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>- (Information not mentioned)</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>- (Information not mentioned)</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>0742 GMT+1</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>3 people: Globetrotter's owner, his son, and his friend</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>- (No deviation mentioned)</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2 minutes</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>- (No distance mentioned)</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>The visibility was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed.</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 1 hour before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident was not mentioned.</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>The vessel's position changed significantly before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Irish Sea</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Wind: easterly Beaufort force 3 to 4, Sea water temperature: 15.3°C</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Running bilge pumps and bailing water out using a bucket</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>RNLI inshore lifeboat</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>cabin space</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Yes, the crew communicated with nearby ships and maritime authorities. The owner alerted both the coastguard and the skipper of "Fivebuoys" by mobile telephone and VHF radio.</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>- (The report does not mention any previous accidents or incidents involving the vessel.)</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>- (The report does not mention any cargo on the vessel.)</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>- (The report does not mention any formal training for the crew in handling emergency situations.)</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>0742</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>3 people: Globetrotter's owner, his son, and his friend</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>- (No deviation mentioned)</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1 hour 10 minutes</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>- (No distance mentioned)</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>The visibility was not explicitly mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed.</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for approximately 1 hour before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident was not mentioned.</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>The change in the vessel's position before and after the incident was significant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Marine Harvest (Scotland) Limited</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kyle of Lochalsh</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>- (No mention of routine activity)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Slowly ahead</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2018.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Yes, there was 1 fatality.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>No, there were no notable mechanical failures reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Yes, a "Mayday" call was received by Stornoway Coastguard at 1520.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Loch Alsh</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Wind: south-westerly at 15 knots, Sea state: slight, Air temperature: 5°C, Water temperature: about 7°C</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>The crew member was attempting to climb on to the feed barge from the workboat Beinn Na Caillich</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>The crew member consumed lunch</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Polarcirkel rigid buoyancy boats (RBB)</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>**Bow door and manoverboard recovery equipment**</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>**Mayday call from the barge on VHF radio channel 16, and shortly afterwards a Mayday call from Beinn Na Caillich**</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>**Emergency drills were rarely conducted on board Beinn Na Caillich and there were no records of them having taken place.**</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>5 people: Beinn Na Caillich's skipper, a deckhand, Stolt Madah's skipper, and two deck crew</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>10 minutes</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>0.5 nautical miles (Beinn Bhreac)</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Visibility: good</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Speed reduction: Yes, the vessel was moving slowly ahead before the incident. The exact percentage decrease in speed is not provided in the context.</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Hours at sea: The context does not provide the exact number of hours the vessel had been at sea before the incident.</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Cargo weight: 570 tons</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Position change: The context does not provide enough information to calculate the distance traveled or the change in latitude/longitude before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Marine Harvest (Scotland) Limited</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kyle of Lochalsh</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>- (No routine activity mentioned)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Slowly ahead</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2018.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Yes, the accident had one fatality.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Yes, a "Mayday" call was sent out at 1520.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Loch Alsh</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Wind: south-westerly at 15 knots, Sea state: slight, Air temperature: 5°C, Water temperature: about 7°C</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>The crew member was involved in a boat transfer from the workboat Beinn Na Caillich to the feed barge.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>The crew member consumed lunch before heading to their post.</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Polarcirkel rigid buoyancy boats (RBB)</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>**Bow door and manoverboard recovery equipment**</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>**Mayday call from the barge and Beinn Na Caillich at 1520**</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>**-**</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>5 people: Beinn Na Caillich's skipper, a deckhand, the assistant manager, and two technicians on the barge.</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>1 hour 10 minutes</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>- (Not mentioned)</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Visibility: good</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Speed reduction: Yes, the vessel was moving slowly ahead. Assuming normal operational speed was 15 knots (from the wind speed given), the vessel was moving at a significantly reduced speed. Exact percentage decrease cannot be calculated without the exact speed at the time of the incident.</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Hours at sea: The vessel had been at sea for approximately 6 hours before the incident. The timeline starts at 0930 when the site manager returned ashore and ends at 1510 when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Cargo weight: 570 tons</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Position change: The vessel was stationary at the time of the incident. Therefore, there was no significant change in position before and after the incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1011:09</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Seadogz Rib Charter Ltd</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Saxon Wharf, Southampton</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>38.4kts (44.2mph)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2012.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Yes, the accident had one fatality.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No, there was no distress signal or emergency call sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>West-south-westerly winds, force 4-5, slight seas, overcast with bright spells, good visibility</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Conducting high speed manoeuvres in close proximity to another vessel</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Rigid Inflatable Boat (RIB) - Seadogz</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>- (No specific mention of safety equipment retrieval in the context)</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>- (No mention of communication with nearby ships or maritime authorities)</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>- (No mention of previous accidents or incidents involving the vessel)</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>- (No mention of cargo on the vessel)</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>- (No specific mention of crew training for emergency situations)</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>10:11:09</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>12 (11 pre-booked passengers and 1 skipper)</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the planned route or deviation)</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the emergency response time)</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the distance to the nearest vessel)</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>The visibility was described as good.</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed. The speed decreased from 44.2 mph (approximately 38.4 knots) to 0 knots upon impact. The percentage decrease in speed is approximately 100%.</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for 1 hour and 19 minutes before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident is not mentioned in the context.</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>The vessel's position changed significantly. The distance traveled before the incident was approximately 10.5 nautical miles (calculated from the time of departure at 0946 to the time of the incident at 1011:09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>pixtral-12b-2409</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1011:09</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Seadogz Rib Charter Ltd</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Saxon Wharf, Southampton</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>38.4kts (44.2mph)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>The vessel was built in 2012.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Yes, the accident had one fatality.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>The vessel was operating under normal conditions when the incident occurred.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>No notable mechanical failures were reported before the incident.</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No, there was no distress signal or emergency call sent out prior to the incident.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>West-south-westerly winds, force 4-5, slight seas, overcast with bright spells, good visibility</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Conducting high speed manoeuvres in close proximity to another vessel</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Rigid Inflatable Boat (RIB) - Seadogz</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>- (No specific mention of safety equipment retrieval in the context)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>- (No mention of communication with nearby ships or maritime authorities)</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>- (No mention of previous accidents or incidents involving the vessel)</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>- (No mention of cargo on the vessel)</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>- (No specific mention of crew training for emergency situations)</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1011:09</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>12 (11 pre-booked passengers and 1 skipper)</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the planned route or deviation)</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the emergency response time)</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>- (The context does not provide information on the distance to the nearest vessel)</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>The visibility was good.</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Yes, the vessel experienced a reduction in speed. The speed decreased from 44.2 mph to 0 mph. The percentage decrease in speed is approximately 100%.</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>The vessel had been at sea for 1 hour and 11 minutes before the incident occurred.</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>The total cargo weight onboard at the time of the incident was not mentioned.</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>The vessel's position changed from Ocean Village marina to the location of the collision with the North-West Netley buoy. The distance traveled is not mentioned in nautical miles or latitude/longitude.</t>
         </is>
       </c>
     </row>
